--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B5" t="n">
-        <v>98505</v>
+        <v>98590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R5" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B6" t="n">
-        <v>98590</v>
+        <v>98505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R6" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2089,7 +2089,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711263</v>
+        <v>128711256</v>
       </c>
       <c r="B16" t="n">
         <v>98590</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517659</v>
+        <v>517653</v>
       </c>
       <c r="R16" t="n">
-        <v>7054360</v>
+        <v>7054410</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711256</v>
+        <v>128711263</v>
       </c>
       <c r="B17" t="n">
         <v>98590</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517653</v>
+        <v>517659</v>
       </c>
       <c r="R17" t="n">
-        <v>7054410</v>
+        <v>7054360</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711220</v>
+        <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98611</v>
+        <v>98505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2430,7 +2430,7 @@
         <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054461</v>
+        <v>7054429</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711217</v>
+        <v>128711220</v>
       </c>
       <c r="B20" t="n">
         <v>98611</v>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R20" t="n">
-        <v>7054465</v>
+        <v>7054461</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711239</v>
+        <v>128711217</v>
       </c>
       <c r="B21" t="n">
-        <v>98505</v>
+        <v>98611</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R21" t="n">
-        <v>7054429</v>
+        <v>7054465</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711225</v>
+        <v>128711271</v>
       </c>
       <c r="B22" t="n">
-        <v>98505</v>
+        <v>98611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517648</v>
+        <v>517655</v>
       </c>
       <c r="R22" t="n">
-        <v>7054446</v>
+        <v>7054394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711271</v>
+        <v>128711225</v>
       </c>
       <c r="B23" t="n">
-        <v>98611</v>
+        <v>98505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517655</v>
+        <v>517648</v>
       </c>
       <c r="R23" t="n">
-        <v>7054394</v>
+        <v>7054446</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98611</v>
+        <v>98505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R28" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98505</v>
+        <v>98611</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R29" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B33" t="n">
-        <v>98611</v>
+        <v>98590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711260</v>
+        <v>128711258</v>
       </c>
       <c r="B34" t="n">
-        <v>98590</v>
+        <v>98611</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B2" t="n">
-        <v>98590</v>
+        <v>98614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R2" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B3" t="n">
-        <v>98611</v>
+        <v>98593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R3" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>128711233</v>
       </c>
       <c r="B4" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B5" t="n">
-        <v>98590</v>
+        <v>98508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R5" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98505</v>
+        <v>98593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R6" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1789,7 +1789,7 @@
         <v>128711255</v>
       </c>
       <c r="B13" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B16" t="n">
-        <v>98590</v>
+        <v>98614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R16" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>128711263</v>
       </c>
       <c r="B17" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B18" t="n">
-        <v>98611</v>
+        <v>98593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R18" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2395,7 +2395,7 @@
         <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711220</v>
+        <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98611</v>
+        <v>98508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R20" t="n">
-        <v>7054461</v>
+        <v>7054446</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711217</v>
+        <v>128711271</v>
       </c>
       <c r="B21" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R21" t="n">
-        <v>7054465</v>
+        <v>7054394</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711271</v>
+        <v>128711220</v>
       </c>
       <c r="B22" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517655</v>
+        <v>517649</v>
       </c>
       <c r="R22" t="n">
-        <v>7054394</v>
+        <v>7054461</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711225</v>
+        <v>128711217</v>
       </c>
       <c r="B23" t="n">
-        <v>98505</v>
+        <v>98614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517648</v>
+        <v>517646</v>
       </c>
       <c r="R23" t="n">
-        <v>7054446</v>
+        <v>7054465</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2900,7 +2900,7 @@
         <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3304,7 +3304,7 @@
         <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3405,7 +3405,7 @@
         <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98590</v>
+        <v>98614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R32" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711260</v>
+        <v>128711244</v>
       </c>
       <c r="B33" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R33" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B34" t="n">
-        <v>98611</v>
+        <v>98593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4016,7 +4016,7 @@
         <v>128711227</v>
       </c>
       <c r="B35" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4117,7 +4117,7 @@
         <v>128711257</v>
       </c>
       <c r="B36" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711258</v>
+        <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98614</v>
+        <v>98593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R32" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711244</v>
+        <v>128711260</v>
       </c>
       <c r="B33" t="n">
         <v>98593</v>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R33" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711260</v>
+        <v>128711258</v>
       </c>
       <c r="B34" t="n">
-        <v>98593</v>
+        <v>98614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98614</v>
+        <v>98594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R2" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98593</v>
+        <v>98615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R3" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>128711233</v>
       </c>
       <c r="B4" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128711245</v>
       </c>
       <c r="B5" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128711216</v>
+        <v>128711255</v>
       </c>
       <c r="B12" t="n">
-        <v>97528</v>
+        <v>98594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517649</v>
+        <v>517658</v>
       </c>
       <c r="R12" t="n">
-        <v>7054471</v>
+        <v>7054404</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128711255</v>
+        <v>128711216</v>
       </c>
       <c r="B13" t="n">
-        <v>98593</v>
+        <v>97529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>222112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517658</v>
+        <v>517649</v>
       </c>
       <c r="R13" t="n">
-        <v>7054404</v>
+        <v>7054471</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1890,7 +1890,7 @@
         <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B16" t="n">
-        <v>98614</v>
+        <v>98594</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R16" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2193,7 +2193,7 @@
         <v>128711263</v>
       </c>
       <c r="B17" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98593</v>
+        <v>98615</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R18" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2395,7 +2395,7 @@
         <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>128711271</v>
       </c>
       <c r="B21" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>128711220</v>
       </c>
       <c r="B22" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>128711217</v>
       </c>
       <c r="B23" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98593</v>
+        <v>98615</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R32" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711260</v>
+        <v>128711244</v>
       </c>
       <c r="B33" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R33" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B34" t="n">
-        <v>98614</v>
+        <v>98594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B35" t="n">
-        <v>98508</v>
+        <v>98615</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R35" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B36" t="n">
-        <v>98614</v>
+        <v>98509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R36" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128711233</v>
       </c>
       <c r="B4" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B5" t="n">
-        <v>98509</v>
+        <v>98621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R5" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B6" t="n">
-        <v>98594</v>
+        <v>98536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R6" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128711255</v>
       </c>
       <c r="B12" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>128711216</v>
       </c>
       <c r="B13" t="n">
-        <v>97529</v>
+        <v>97556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711256</v>
+        <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517653</v>
+        <v>517659</v>
       </c>
       <c r="R16" t="n">
-        <v>7054410</v>
+        <v>7054360</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711263</v>
+        <v>128711256</v>
       </c>
       <c r="B17" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517659</v>
+        <v>517653</v>
       </c>
       <c r="R17" t="n">
-        <v>7054360</v>
+        <v>7054410</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2294,7 +2294,7 @@
         <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711239</v>
+        <v>128711271</v>
       </c>
       <c r="B19" t="n">
-        <v>98509</v>
+        <v>98642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517649</v>
+        <v>517655</v>
       </c>
       <c r="R19" t="n">
-        <v>7054429</v>
+        <v>7054394</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B20" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R20" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711271</v>
+        <v>128711225</v>
       </c>
       <c r="B21" t="n">
-        <v>98615</v>
+        <v>98536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517655</v>
+        <v>517648</v>
       </c>
       <c r="R21" t="n">
-        <v>7054394</v>
+        <v>7054446</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>128711220</v>
       </c>
       <c r="B22" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>128711217</v>
       </c>
       <c r="B23" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>128711234</v>
       </c>
       <c r="B30" t="n">
-        <v>43026</v>
+        <v>43053</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711258</v>
+        <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98615</v>
+        <v>98621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R32" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B33" t="n">
-        <v>98594</v>
+        <v>98642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R33" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3915,7 +3915,7 @@
         <v>128711260</v>
       </c>
       <c r="B34" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128711257</v>
       </c>
       <c r="B35" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128711227</v>
       </c>
       <c r="B36" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R2" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B3" t="n">
-        <v>98642</v>
+        <v>98621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R3" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B8" t="n">
-        <v>98621</v>
+        <v>98642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R8" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B9" t="n">
-        <v>98642</v>
+        <v>98621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R9" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1887,7 +1887,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128711242</v>
+        <v>128711221</v>
       </c>
       <c r="B14" t="n">
         <v>98536</v>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R14" t="n">
-        <v>7054421</v>
+        <v>7054459</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128711221</v>
+        <v>128711242</v>
       </c>
       <c r="B15" t="n">
         <v>98536</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R15" t="n">
-        <v>7054459</v>
+        <v>7054421</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711263</v>
+        <v>128711235</v>
       </c>
       <c r="B16" t="n">
-        <v>98621</v>
+        <v>98642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517659</v>
+        <v>517650</v>
       </c>
       <c r="R16" t="n">
-        <v>7054360</v>
+        <v>7054437</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711256</v>
+        <v>128711263</v>
       </c>
       <c r="B17" t="n">
         <v>98621</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517653</v>
+        <v>517659</v>
       </c>
       <c r="R17" t="n">
-        <v>7054410</v>
+        <v>7054360</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B18" t="n">
-        <v>98642</v>
+        <v>98621</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R18" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711271</v>
+        <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98642</v>
+        <v>98536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517655</v>
+        <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054394</v>
+        <v>7054429</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711239</v>
+        <v>128711220</v>
       </c>
       <c r="B20" t="n">
-        <v>98536</v>
+        <v>98642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>517649</v>
       </c>
       <c r="R20" t="n">
-        <v>7054429</v>
+        <v>7054461</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711225</v>
+        <v>128711217</v>
       </c>
       <c r="B21" t="n">
-        <v>98536</v>
+        <v>98642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517648</v>
+        <v>517646</v>
       </c>
       <c r="R21" t="n">
-        <v>7054446</v>
+        <v>7054465</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,7 +2695,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711220</v>
+        <v>128711271</v>
       </c>
       <c r="B22" t="n">
         <v>98642</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517649</v>
+        <v>517655</v>
       </c>
       <c r="R22" t="n">
-        <v>7054461</v>
+        <v>7054394</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711217</v>
+        <v>128711225</v>
       </c>
       <c r="B23" t="n">
-        <v>98642</v>
+        <v>98536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517646</v>
+        <v>517648</v>
       </c>
       <c r="R23" t="n">
-        <v>7054465</v>
+        <v>7054446</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B28" t="n">
-        <v>98536</v>
+        <v>98642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R28" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B29" t="n">
-        <v>98642</v>
+        <v>98536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R29" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98621</v>
+        <v>98642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R32" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711258</v>
+        <v>128711244</v>
       </c>
       <c r="B33" t="n">
-        <v>98642</v>
+        <v>98621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R33" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98642</v>
+        <v>98627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R2" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R3" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128711233</v>
+        <v>128711245</v>
       </c>
       <c r="B4" t="n">
-        <v>98621</v>
+        <v>98542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>517650</v>
       </c>
       <c r="R4" t="n">
-        <v>7054437</v>
+        <v>7054420</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711254</v>
+        <v>128711233</v>
       </c>
       <c r="B5" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R5" t="n">
-        <v>7054414</v>
+        <v>7054437</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98536</v>
+        <v>98627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R6" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98642</v>
+        <v>98627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R8" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R9" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128711255</v>
+        <v>128711216</v>
       </c>
       <c r="B12" t="n">
-        <v>98621</v>
+        <v>97562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>222112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517658</v>
+        <v>517649</v>
       </c>
       <c r="R12" t="n">
-        <v>7054404</v>
+        <v>7054471</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128711216</v>
+        <v>128711255</v>
       </c>
       <c r="B13" t="n">
-        <v>97556</v>
+        <v>98627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517649</v>
+        <v>517658</v>
       </c>
       <c r="R13" t="n">
-        <v>7054471</v>
+        <v>7054404</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128711221</v>
+        <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R14" t="n">
-        <v>7054459</v>
+        <v>7054421</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128711242</v>
+        <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R15" t="n">
-        <v>7054421</v>
+        <v>7054459</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711235</v>
+        <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98642</v>
+        <v>98627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517650</v>
+        <v>517659</v>
       </c>
       <c r="R16" t="n">
-        <v>7054437</v>
+        <v>7054360</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711263</v>
+        <v>128711256</v>
       </c>
       <c r="B17" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517659</v>
+        <v>517653</v>
       </c>
       <c r="R17" t="n">
-        <v>7054360</v>
+        <v>7054410</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R18" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2395,7 +2395,7 @@
         <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711220</v>
+        <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98642</v>
+        <v>98542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R20" t="n">
-        <v>7054461</v>
+        <v>7054446</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711217</v>
+        <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R21" t="n">
-        <v>7054465</v>
+        <v>7054461</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711271</v>
+        <v>128711217</v>
       </c>
       <c r="B22" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R22" t="n">
-        <v>7054394</v>
+        <v>7054465</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711225</v>
+        <v>128711271</v>
       </c>
       <c r="B23" t="n">
-        <v>98536</v>
+        <v>98648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517648</v>
+        <v>517655</v>
       </c>
       <c r="R23" t="n">
-        <v>7054446</v>
+        <v>7054394</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711266</v>
+        <v>128711264</v>
       </c>
       <c r="B24" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517656</v>
+        <v>517658</v>
       </c>
       <c r="R24" t="n">
-        <v>7054391</v>
+        <v>7054379</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711264</v>
+        <v>128711266</v>
       </c>
       <c r="B25" t="n">
-        <v>98642</v>
+        <v>98627</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517658</v>
+        <v>517656</v>
       </c>
       <c r="R25" t="n">
-        <v>7054379</v>
+        <v>7054391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98642</v>
+        <v>98542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R28" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98536</v>
+        <v>98648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R29" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711258</v>
+        <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98642</v>
+        <v>98627</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R32" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B33" t="n">
-        <v>98621</v>
+        <v>98648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R33" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3915,7 +3915,7 @@
         <v>128711260</v>
       </c>
       <c r="B34" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B35" t="n">
-        <v>98642</v>
+        <v>98542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R35" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B36" t="n">
-        <v>98536</v>
+        <v>98648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R36" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98674</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R2" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R3" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98674</v>
+        <v>98653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R8" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98653</v>
+        <v>98674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R9" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711263</v>
+        <v>128711235</v>
       </c>
       <c r="B16" t="n">
-        <v>98653</v>
+        <v>98674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517659</v>
+        <v>517650</v>
       </c>
       <c r="R16" t="n">
-        <v>7054360</v>
+        <v>7054437</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711256</v>
+        <v>128711263</v>
       </c>
       <c r="B17" t="n">
         <v>98653</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517653</v>
+        <v>517659</v>
       </c>
       <c r="R17" t="n">
-        <v>7054410</v>
+        <v>7054360</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B18" t="n">
-        <v>98674</v>
+        <v>98653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R18" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128711245</v>
       </c>
       <c r="B4" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128711233</v>
       </c>
       <c r="B5" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128711216</v>
+        <v>128711255</v>
       </c>
       <c r="B12" t="n">
-        <v>97588</v>
+        <v>98658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517649</v>
+        <v>517658</v>
       </c>
       <c r="R12" t="n">
-        <v>7054471</v>
+        <v>7054404</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128711255</v>
+        <v>128711216</v>
       </c>
       <c r="B13" t="n">
-        <v>98653</v>
+        <v>97593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>222112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517658</v>
+        <v>517649</v>
       </c>
       <c r="R13" t="n">
-        <v>7054404</v>
+        <v>7054471</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128711242</v>
+        <v>128711221</v>
       </c>
       <c r="B14" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R14" t="n">
-        <v>7054421</v>
+        <v>7054459</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128711221</v>
+        <v>128711242</v>
       </c>
       <c r="B15" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R15" t="n">
-        <v>7054459</v>
+        <v>7054421</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711235</v>
+        <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98674</v>
+        <v>98658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517650</v>
+        <v>517659</v>
       </c>
       <c r="R16" t="n">
-        <v>7054437</v>
+        <v>7054360</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711263</v>
+        <v>128711256</v>
       </c>
       <c r="B17" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517659</v>
+        <v>517653</v>
       </c>
       <c r="R17" t="n">
-        <v>7054360</v>
+        <v>7054410</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98653</v>
+        <v>98679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R18" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711239</v>
+        <v>128711225</v>
       </c>
       <c r="B19" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R19" t="n">
-        <v>7054429</v>
+        <v>7054446</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B20" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R20" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2597,7 +2597,7 @@
         <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>128711217</v>
       </c>
       <c r="B22" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>128711271</v>
       </c>
       <c r="B23" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98674</v>
+        <v>98679</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98653</v>
+        <v>98658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B33" t="n">
-        <v>98674</v>
+        <v>98658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711260</v>
+        <v>128711258</v>
       </c>
       <c r="B34" t="n">
-        <v>98653</v>
+        <v>98679</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B35" t="n">
-        <v>98568</v>
+        <v>98679</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R35" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B36" t="n">
-        <v>98674</v>
+        <v>98573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R36" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>128711245</v>
       </c>
       <c r="B4" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -981,7 +981,7 @@
         <v>128711233</v>
       </c>
       <c r="B5" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1688,7 +1688,7 @@
         <v>128711255</v>
       </c>
       <c r="B12" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1789,7 +1789,7 @@
         <v>128711216</v>
       </c>
       <c r="B13" t="n">
-        <v>97593</v>
+        <v>97596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128711221</v>
+        <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R14" t="n">
-        <v>7054459</v>
+        <v>7054421</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128711242</v>
+        <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R15" t="n">
-        <v>7054421</v>
+        <v>7054459</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2092,7 +2092,7 @@
         <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B17" t="n">
-        <v>98658</v>
+        <v>98682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R17" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B18" t="n">
-        <v>98679</v>
+        <v>98661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R18" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711239</v>
+        <v>128711271</v>
       </c>
       <c r="B20" t="n">
-        <v>98573</v>
+        <v>98682</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517649</v>
+        <v>517655</v>
       </c>
       <c r="R20" t="n">
-        <v>7054429</v>
+        <v>7054394</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2597,7 +2597,7 @@
         <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>128711217</v>
       </c>
       <c r="B22" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711271</v>
+        <v>128711225</v>
       </c>
       <c r="B23" t="n">
-        <v>98679</v>
+        <v>98576</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517655</v>
+        <v>517648</v>
       </c>
       <c r="R23" t="n">
-        <v>7054394</v>
+        <v>7054446</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711266</v>
+        <v>128711264</v>
       </c>
       <c r="B24" t="n">
-        <v>98658</v>
+        <v>98682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517656</v>
+        <v>517658</v>
       </c>
       <c r="R24" t="n">
-        <v>7054391</v>
+        <v>7054379</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711264</v>
+        <v>128711266</v>
       </c>
       <c r="B25" t="n">
-        <v>98679</v>
+        <v>98661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517658</v>
+        <v>517656</v>
       </c>
       <c r="R25" t="n">
-        <v>7054379</v>
+        <v>7054391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B28" t="n">
-        <v>98573</v>
+        <v>98682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R28" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B29" t="n">
-        <v>98679</v>
+        <v>98576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R29" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3713,7 +3713,7 @@
         <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98658</v>
+        <v>98661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711260</v>
+        <v>128711258</v>
       </c>
       <c r="B33" t="n">
-        <v>98658</v>
+        <v>98682</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B34" t="n">
-        <v>98679</v>
+        <v>98661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4016,7 +4016,7 @@
         <v>128711257</v>
       </c>
       <c r="B35" t="n">
-        <v>98679</v>
+        <v>98682</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4117,7 +4117,7 @@
         <v>128711227</v>
       </c>
       <c r="B36" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128711245</v>
+        <v>128711233</v>
       </c>
       <c r="B4" t="n">
-        <v>98576</v>
+        <v>98661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>517650</v>
       </c>
       <c r="R4" t="n">
-        <v>7054420</v>
+        <v>7054437</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711233</v>
+        <v>128711254</v>
       </c>
       <c r="B5" t="n">
         <v>98661</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R5" t="n">
-        <v>7054437</v>
+        <v>7054414</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B6" t="n">
-        <v>98661</v>
+        <v>98576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R6" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B8" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R8" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B9" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R9" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128711255</v>
+        <v>128711216</v>
       </c>
       <c r="B12" t="n">
-        <v>98661</v>
+        <v>97596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>222112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517658</v>
+        <v>517649</v>
       </c>
       <c r="R12" t="n">
-        <v>7054404</v>
+        <v>7054471</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128711216</v>
+        <v>128711255</v>
       </c>
       <c r="B13" t="n">
-        <v>97596</v>
+        <v>98661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517649</v>
+        <v>517658</v>
       </c>
       <c r="R13" t="n">
-        <v>7054471</v>
+        <v>7054404</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98682</v>
+        <v>98576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R28" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98576</v>
+        <v>98682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R29" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R32" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B33" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711260</v>
+        <v>128711244</v>
       </c>
       <c r="B34" t="n">
         <v>98661</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R34" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B5" t="n">
-        <v>98661</v>
+        <v>98576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R5" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98576</v>
+        <v>98661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R6" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R8" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R9" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711263</v>
+        <v>128711235</v>
       </c>
       <c r="B16" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517659</v>
+        <v>517650</v>
       </c>
       <c r="R16" t="n">
-        <v>7054360</v>
+        <v>7054437</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711235</v>
+        <v>128711263</v>
       </c>
       <c r="B17" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517650</v>
+        <v>517659</v>
       </c>
       <c r="R17" t="n">
-        <v>7054437</v>
+        <v>7054360</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711239</v>
+        <v>128711220</v>
       </c>
       <c r="B19" t="n">
-        <v>98576</v>
+        <v>98682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2430,7 +2430,7 @@
         <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054429</v>
+        <v>7054461</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711271</v>
+        <v>128711217</v>
       </c>
       <c r="B20" t="n">
         <v>98682</v>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R20" t="n">
-        <v>7054394</v>
+        <v>7054465</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2594,7 +2594,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711220</v>
+        <v>128711271</v>
       </c>
       <c r="B21" t="n">
         <v>98682</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517649</v>
+        <v>517655</v>
       </c>
       <c r="R21" t="n">
-        <v>7054461</v>
+        <v>7054394</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711217</v>
+        <v>128711225</v>
       </c>
       <c r="B22" t="n">
-        <v>98682</v>
+        <v>98576</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517646</v>
+        <v>517648</v>
       </c>
       <c r="R22" t="n">
-        <v>7054465</v>
+        <v>7054446</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B23" t="n">
         <v>98576</v>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R23" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711264</v>
+        <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517658</v>
+        <v>517656</v>
       </c>
       <c r="R24" t="n">
-        <v>7054379</v>
+        <v>7054391</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2998,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711266</v>
+        <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517656</v>
+        <v>517658</v>
       </c>
       <c r="R25" t="n">
-        <v>7054391</v>
+        <v>7054379</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3811,7 +3811,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711260</v>
+        <v>128711244</v>
       </c>
       <c r="B33" t="n">
         <v>98661</v>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R33" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711244</v>
+        <v>128711260</v>
       </c>
       <c r="B34" t="n">
         <v>98661</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R34" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B35" t="n">
-        <v>98682</v>
+        <v>98576</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R35" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B36" t="n">
-        <v>98576</v>
+        <v>98682</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R36" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B2" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R2" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B3" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R3" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B8" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R8" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B9" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R9" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711235</v>
+        <v>128711256</v>
       </c>
       <c r="B16" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R16" t="n">
-        <v>7054437</v>
+        <v>7054410</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711256</v>
+        <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R18" t="n">
-        <v>7054410</v>
+        <v>7054437</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,7 +2695,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B22" t="n">
         <v>98576</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R22" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2796,7 +2796,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711239</v>
+        <v>128711225</v>
       </c>
       <c r="B23" t="n">
         <v>98576</v>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R23" t="n">
-        <v>7054429</v>
+        <v>7054446</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711266</v>
+        <v>128711264</v>
       </c>
       <c r="B24" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517656</v>
+        <v>517658</v>
       </c>
       <c r="R24" t="n">
-        <v>7054391</v>
+        <v>7054379</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2998,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711264</v>
+        <v>128711266</v>
       </c>
       <c r="B25" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517658</v>
+        <v>517656</v>
       </c>
       <c r="R25" t="n">
-        <v>7054379</v>
+        <v>7054391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B28" t="n">
-        <v>98576</v>
+        <v>98682</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R28" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B29" t="n">
-        <v>98682</v>
+        <v>98576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R29" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711258</v>
+        <v>128711244</v>
       </c>
       <c r="B32" t="n">
-        <v>98682</v>
+        <v>98661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R32" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B33" t="n">
-        <v>98661</v>
+        <v>98682</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R33" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B35" t="n">
-        <v>98576</v>
+        <v>98682</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R35" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B36" t="n">
-        <v>98682</v>
+        <v>98576</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R36" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128711251</v>
       </c>
       <c r="B2" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128711243</v>
       </c>
       <c r="B3" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128711233</v>
       </c>
       <c r="B4" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B5" t="n">
-        <v>98576</v>
+        <v>98671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R5" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711254</v>
+        <v>128711245</v>
       </c>
       <c r="B6" t="n">
-        <v>98661</v>
+        <v>98586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R6" t="n">
-        <v>7054414</v>
+        <v>7054420</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711250</v>
+        <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98682</v>
+        <v>98671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517655</v>
+        <v>517646</v>
       </c>
       <c r="R8" t="n">
-        <v>7054413</v>
+        <v>7054461</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711219</v>
+        <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98661</v>
+        <v>98692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517646</v>
+        <v>517655</v>
       </c>
       <c r="R9" t="n">
-        <v>7054461</v>
+        <v>7054413</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128711216</v>
       </c>
       <c r="B12" t="n">
-        <v>97596</v>
+        <v>97606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>128711255</v>
       </c>
       <c r="B13" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711256</v>
+        <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517653</v>
+        <v>517659</v>
       </c>
       <c r="R16" t="n">
-        <v>7054410</v>
+        <v>7054360</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711263</v>
+        <v>128711256</v>
       </c>
       <c r="B17" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517659</v>
+        <v>517653</v>
       </c>
       <c r="R17" t="n">
-        <v>7054360</v>
+        <v>7054410</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2294,7 +2294,7 @@
         <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711220</v>
+        <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98682</v>
+        <v>98586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2430,7 +2430,7 @@
         <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054461</v>
+        <v>7054429</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711217</v>
+        <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98682</v>
+        <v>98586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517646</v>
+        <v>517648</v>
       </c>
       <c r="R20" t="n">
-        <v>7054465</v>
+        <v>7054446</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711271</v>
+        <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517655</v>
+        <v>517649</v>
       </c>
       <c r="R21" t="n">
-        <v>7054394</v>
+        <v>7054461</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2695,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711239</v>
+        <v>128711217</v>
       </c>
       <c r="B22" t="n">
-        <v>98576</v>
+        <v>98692</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,21 +2706,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R22" t="n">
-        <v>7054429</v>
+        <v>7054465</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711225</v>
+        <v>128711271</v>
       </c>
       <c r="B23" t="n">
-        <v>98576</v>
+        <v>98692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517648</v>
+        <v>517655</v>
       </c>
       <c r="R23" t="n">
-        <v>7054446</v>
+        <v>7054394</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711264</v>
+        <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98682</v>
+        <v>98671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517658</v>
+        <v>517656</v>
       </c>
       <c r="R24" t="n">
-        <v>7054379</v>
+        <v>7054391</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2998,10 +2998,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711266</v>
+        <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98661</v>
+        <v>98692</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517656</v>
+        <v>517658</v>
       </c>
       <c r="R25" t="n">
-        <v>7054391</v>
+        <v>7054379</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B28" t="n">
-        <v>98682</v>
+        <v>98586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R28" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B29" t="n">
-        <v>98576</v>
+        <v>98692</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R29" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711244</v>
+        <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98661</v>
+        <v>98692</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517650</v>
+        <v>517656</v>
       </c>
       <c r="R32" t="n">
-        <v>7054421</v>
+        <v>7054401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711258</v>
+        <v>128711260</v>
       </c>
       <c r="B33" t="n">
-        <v>98682</v>
+        <v>98671</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711260</v>
+        <v>128711244</v>
       </c>
       <c r="B34" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517656</v>
+        <v>517650</v>
       </c>
       <c r="R34" t="n">
-        <v>7054401</v>
+        <v>7054421</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4013,10 +4013,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711257</v>
+        <v>128711227</v>
       </c>
       <c r="B35" t="n">
-        <v>98682</v>
+        <v>98586</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4024,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517654</v>
+        <v>517647</v>
       </c>
       <c r="R35" t="n">
-        <v>7054407</v>
+        <v>7054446</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711227</v>
+        <v>128711257</v>
       </c>
       <c r="B36" t="n">
-        <v>98576</v>
+        <v>98692</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517647</v>
+        <v>517654</v>
       </c>
       <c r="R36" t="n">
-        <v>7054446</v>
+        <v>7054407</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128711233</v>
+        <v>128711245</v>
       </c>
       <c r="B4" t="n">
-        <v>98671</v>
+        <v>98586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>517650</v>
       </c>
       <c r="R4" t="n">
-        <v>7054437</v>
+        <v>7054420</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711254</v>
+        <v>128711233</v>
       </c>
       <c r="B5" t="n">
         <v>98671</v>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517653</v>
+        <v>517650</v>
       </c>
       <c r="R5" t="n">
-        <v>7054414</v>
+        <v>7054437</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711245</v>
+        <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98586</v>
+        <v>98671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R6" t="n">
-        <v>7054420</v>
+        <v>7054414</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711239</v>
+        <v>128711217</v>
       </c>
       <c r="B19" t="n">
-        <v>98586</v>
+        <v>98692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R19" t="n">
-        <v>7054429</v>
+        <v>7054465</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711225</v>
+        <v>128711239</v>
       </c>
       <c r="B20" t="n">
         <v>98586</v>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R20" t="n">
-        <v>7054446</v>
+        <v>7054429</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711220</v>
+        <v>128711225</v>
       </c>
       <c r="B21" t="n">
-        <v>98692</v>
+        <v>98586</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R21" t="n">
-        <v>7054461</v>
+        <v>7054446</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,7 +2695,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711217</v>
+        <v>128711220</v>
       </c>
       <c r="B22" t="n">
         <v>98692</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R22" t="n">
-        <v>7054465</v>
+        <v>7054461</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -2392,10 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711217</v>
+        <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98692</v>
+        <v>98586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R19" t="n">
-        <v>7054465</v>
+        <v>7054429</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128711239</v>
+        <v>128711225</v>
       </c>
       <c r="B20" t="n">
         <v>98586</v>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517649</v>
+        <v>517648</v>
       </c>
       <c r="R20" t="n">
-        <v>7054429</v>
+        <v>7054446</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711225</v>
+        <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98586</v>
+        <v>98692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517648</v>
+        <v>517649</v>
       </c>
       <c r="R21" t="n">
-        <v>7054446</v>
+        <v>7054461</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,7 +2695,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711220</v>
+        <v>128711217</v>
       </c>
       <c r="B22" t="n">
         <v>98692</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R22" t="n">
-        <v>7054461</v>
+        <v>7054465</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711251</v>
+        <v>128711243</v>
       </c>
       <c r="B2" t="n">
-        <v>98692</v>
+        <v>98680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517654</v>
+        <v>517649</v>
       </c>
       <c r="R2" t="n">
-        <v>7054417</v>
+        <v>7054428</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711243</v>
+        <v>128711251</v>
       </c>
       <c r="B3" t="n">
-        <v>98671</v>
+        <v>98701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517649</v>
+        <v>517654</v>
       </c>
       <c r="R3" t="n">
-        <v>7054428</v>
+        <v>7054417</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>128711245</v>
       </c>
       <c r="B4" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128711233</v>
       </c>
       <c r="B5" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128711254</v>
       </c>
       <c r="B6" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128711224</v>
       </c>
       <c r="B7" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128711219</v>
       </c>
       <c r="B8" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128711250</v>
       </c>
       <c r="B9" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128711229</v>
       </c>
       <c r="B10" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128711265</v>
       </c>
       <c r="B11" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128711216</v>
       </c>
       <c r="B12" t="n">
-        <v>97606</v>
+        <v>97615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>128711255</v>
       </c>
       <c r="B13" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>128711242</v>
       </c>
       <c r="B14" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128711221</v>
       </c>
       <c r="B15" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>128711263</v>
       </c>
       <c r="B16" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>128711256</v>
       </c>
       <c r="B17" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>128711235</v>
       </c>
       <c r="B18" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>128711239</v>
       </c>
       <c r="B19" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>128711220</v>
       </c>
       <c r="B21" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>128711217</v>
       </c>
       <c r="B22" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>128711271</v>
       </c>
       <c r="B23" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>128711266</v>
       </c>
       <c r="B24" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>128711264</v>
       </c>
       <c r="B25" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128711238</v>
       </c>
       <c r="B26" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128711228</v>
       </c>
       <c r="B27" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711218</v>
+        <v>128711226</v>
       </c>
       <c r="B28" t="n">
-        <v>98586</v>
+        <v>98701</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517646</v>
+        <v>517649</v>
       </c>
       <c r="R28" t="n">
-        <v>7054465</v>
+        <v>7054451</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711226</v>
+        <v>128711218</v>
       </c>
       <c r="B29" t="n">
-        <v>98692</v>
+        <v>98595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,21 +3413,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517649</v>
+        <v>517646</v>
       </c>
       <c r="R29" t="n">
-        <v>7054451</v>
+        <v>7054465</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3612,7 +3612,7 @@
         <v>128711247</v>
       </c>
       <c r="B31" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>128711258</v>
       </c>
       <c r="B32" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>128711260</v>
       </c>
       <c r="B33" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128711244</v>
       </c>
       <c r="B34" t="n">
-        <v>98671</v>
+        <v>98680</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128711227</v>
       </c>
       <c r="B35" t="n">
-        <v>98586</v>
+        <v>98595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>128711257</v>
       </c>
       <c r="B36" t="n">
-        <v>98692</v>
+        <v>98701</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4212,6 +4212,118 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130055222</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97735</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hammerdal-Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7054471</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -4218,7 +4218,7 @@
         <v>130055222</v>
       </c>
       <c r="B37" t="n">
-        <v>97735</v>
+        <v>97752</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -4218,7 +4218,7 @@
         <v>130055222</v>
       </c>
       <c r="B37" t="n">
-        <v>97768</v>
+        <v>97770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -4218,7 +4218,7 @@
         <v>130055222</v>
       </c>
       <c r="B37" t="n">
-        <v>97770</v>
+        <v>97857</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128711243</v>
+        <v>125950641</v>
       </c>
       <c r="B2" t="n">
-        <v>98680</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+          <t>Vägkant västersida, Sikåsån, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517649</v>
+        <v>517711</v>
       </c>
       <c r="R2" t="n">
-        <v>7054428</v>
+        <v>7054188</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,54 +770,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Elisabeth Olsson Hedin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Elisabeth Olsson Hedin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128711251</v>
+        <v>128711234</v>
       </c>
       <c r="B3" t="n">
-        <v>98701</v>
+        <v>43249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>101248</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517654</v>
+        <v>517648</v>
       </c>
       <c r="R3" t="n">
-        <v>7054417</v>
+        <v>7054436</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -849,6 +862,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ägg</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128711245</v>
+        <v>128711262</v>
       </c>
       <c r="B4" t="n">
-        <v>98595</v>
+        <v>43249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>101248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517650</v>
+        <v>517657</v>
       </c>
       <c r="R4" t="n">
-        <v>7054420</v>
+        <v>7054364</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -950,6 +968,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -967,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128711233</v>
+        <v>128711270</v>
       </c>
       <c r="B5" t="n">
-        <v>98680</v>
+        <v>43249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>101248</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517650</v>
+        <v>517653</v>
       </c>
       <c r="R5" t="n">
-        <v>7054437</v>
+        <v>7054389</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,6 +1074,11 @@
           <t>2025-06-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ägg</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128711254</v>
+        <v>133021108</v>
       </c>
       <c r="B6" t="n">
-        <v>98680</v>
+        <v>57153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,37 +1118,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+          <t>Vägkant västersida, Sikåsån, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517653</v>
+        <v>517711</v>
       </c>
       <c r="R6" t="n">
-        <v>7054414</v>
+        <v>7054188</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1144,12 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,26 +1200,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Elisabeth Olsson Hedin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
-        </is>
-      </c>
+          <t>Elisabeth Olsson Hedin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128711224</v>
+        <v>128710851</v>
       </c>
       <c r="B7" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517651</v>
+        <v>517630</v>
       </c>
       <c r="R7" t="n">
-        <v>7054454</v>
+        <v>7054448</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1245,12 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1302,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1281,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128711219</v>
+        <v>128710855</v>
       </c>
       <c r="B8" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1324,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517646</v>
+        <v>517634</v>
       </c>
       <c r="R8" t="n">
-        <v>7054461</v>
+        <v>7054446</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1346,12 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1371,7 +1403,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128711250</v>
+        <v>128710860</v>
       </c>
       <c r="B9" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517655</v>
+        <v>517632</v>
       </c>
       <c r="R9" t="n">
-        <v>7054413</v>
+        <v>7054444</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1447,12 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1472,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1483,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128711229</v>
+        <v>128710867</v>
       </c>
       <c r="B10" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517648</v>
+        <v>517637</v>
       </c>
       <c r="R10" t="n">
-        <v>7054440</v>
+        <v>7054435</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,12 +1580,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1605,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1584,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128711265</v>
+        <v>128710868</v>
       </c>
       <c r="B11" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517657</v>
+        <v>517632</v>
       </c>
       <c r="R11" t="n">
-        <v>7054379</v>
+        <v>7054437</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1649,12 +1681,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1717,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128711216</v>
+        <v>128710874</v>
       </c>
       <c r="B12" t="n">
-        <v>97615</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222112</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517649</v>
+        <v>517633</v>
       </c>
       <c r="R12" t="n">
-        <v>7054471</v>
+        <v>7054432</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1750,12 +1782,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128711255</v>
+        <v>128710877</v>
       </c>
       <c r="B13" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517658</v>
+        <v>517632</v>
       </c>
       <c r="R13" t="n">
-        <v>7054404</v>
+        <v>7054429</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1851,12 +1883,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1876,7 +1908,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1887,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128711242</v>
+        <v>128710880</v>
       </c>
       <c r="B14" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517655</v>
+        <v>517635</v>
       </c>
       <c r="R14" t="n">
-        <v>7054421</v>
+        <v>7054428</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1952,12 +1984,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1988,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128711221</v>
+        <v>128710884</v>
       </c>
       <c r="B15" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517646</v>
+        <v>517637</v>
       </c>
       <c r="R15" t="n">
-        <v>7054459</v>
+        <v>7054424</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2053,12 +2085,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,7 +2110,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2089,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128711263</v>
+        <v>128711218</v>
       </c>
       <c r="B16" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517659</v>
+        <v>517646</v>
       </c>
       <c r="R16" t="n">
-        <v>7054360</v>
+        <v>7054465</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2190,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128711256</v>
+        <v>128711221</v>
       </c>
       <c r="B17" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2233,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517653</v>
+        <v>517646</v>
       </c>
       <c r="R17" t="n">
-        <v>7054410</v>
+        <v>7054459</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2291,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128711235</v>
+        <v>128711223</v>
       </c>
       <c r="B18" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2334,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517650</v>
+        <v>517645</v>
       </c>
       <c r="R18" t="n">
-        <v>7054437</v>
+        <v>7054455</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2381,7 +2413,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2392,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128711239</v>
+        <v>128711224</v>
       </c>
       <c r="B19" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517649</v>
+        <v>517651</v>
       </c>
       <c r="R19" t="n">
-        <v>7054429</v>
+        <v>7054454</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2482,7 +2514,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2496,7 +2528,7 @@
         <v>128711225</v>
       </c>
       <c r="B20" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2594,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128711220</v>
+        <v>128711227</v>
       </c>
       <c r="B21" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2605,21 +2637,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2629,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>517649</v>
+        <v>517647</v>
       </c>
       <c r="R21" t="n">
-        <v>7054461</v>
+        <v>7054446</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2684,7 +2716,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2695,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128711217</v>
+        <v>128711228</v>
       </c>
       <c r="B22" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,21 +2738,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>517646</v>
+        <v>517648</v>
       </c>
       <c r="R22" t="n">
-        <v>7054465</v>
+        <v>7054453</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2817,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2796,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128711271</v>
+        <v>128711230</v>
       </c>
       <c r="B23" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2839,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>517655</v>
+        <v>517647</v>
       </c>
       <c r="R23" t="n">
-        <v>7054394</v>
+        <v>7054439</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2886,7 +2918,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2897,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128711266</v>
+        <v>128711237</v>
       </c>
       <c r="B24" t="n">
-        <v>98680</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>517656</v>
+        <v>517648</v>
       </c>
       <c r="R24" t="n">
-        <v>7054391</v>
+        <v>7054434</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2987,7 +3019,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2998,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128711264</v>
+        <v>128711238</v>
       </c>
       <c r="B25" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,21 +3041,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3033,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>517658</v>
+        <v>517651</v>
       </c>
       <c r="R25" t="n">
-        <v>7054379</v>
+        <v>7054433</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3088,7 +3120,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3099,10 +3131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128711238</v>
+        <v>128711239</v>
       </c>
       <c r="B26" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>517651</v>
+        <v>517649</v>
       </c>
       <c r="R26" t="n">
-        <v>7054433</v>
+        <v>7054429</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3189,7 +3221,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3200,10 +3232,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128711228</v>
+        <v>128711242</v>
       </c>
       <c r="B27" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517648</v>
+        <v>517655</v>
       </c>
       <c r="R27" t="n">
-        <v>7054453</v>
+        <v>7054421</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3301,10 +3333,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128711226</v>
+        <v>128711245</v>
       </c>
       <c r="B28" t="n">
-        <v>98701</v>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517649</v>
+        <v>517650</v>
       </c>
       <c r="R28" t="n">
-        <v>7054451</v>
+        <v>7054420</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3391,7 +3423,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3402,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128711218</v>
+        <v>128711252</v>
       </c>
       <c r="B29" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3437,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517646</v>
+        <v>517650</v>
       </c>
       <c r="R29" t="n">
-        <v>7054465</v>
+        <v>7054413</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3503,32 +3535,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128711234</v>
+        <v>128710856</v>
       </c>
       <c r="B30" t="n">
-        <v>43056</v>
+        <v>99120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101248</v>
+        <v>219811</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3538,10 +3570,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>517648</v>
+        <v>517632</v>
       </c>
       <c r="R30" t="n">
-        <v>7054436</v>
+        <v>7054444</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3568,17 +3600,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ägg</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3598,7 +3625,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3609,10 +3636,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128711247</v>
+        <v>128710858</v>
       </c>
       <c r="B31" t="n">
-        <v>98680</v>
+        <v>99120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>517656</v>
+        <v>517628</v>
       </c>
       <c r="R31" t="n">
-        <v>7054411</v>
+        <v>7054440</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3674,12 +3701,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3699,7 +3726,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Borgström, Magnus Lundin</t>
+          <t>Magnus Lundin, Erik Borgström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3710,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128711258</v>
+        <v>128710859</v>
       </c>
       <c r="B32" t="n">
-        <v>98701</v>
+        <v>99120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3748,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3772,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>517656</v>
+        <v>517630</v>
       </c>
       <c r="R32" t="n">
-        <v>7054401</v>
+        <v>7054443</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3775,12 +3802,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3811,10 +3838,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128711260</v>
+        <v>128710862</v>
       </c>
       <c r="B33" t="n">
-        <v>98680</v>
+        <v>99120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,10 +3873,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>517656</v>
+        <v>517632</v>
       </c>
       <c r="R33" t="n">
-        <v>7054401</v>
+        <v>7054439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3876,12 +3903,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3912,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128711244</v>
+        <v>128710863</v>
       </c>
       <c r="B34" t="n">
-        <v>98680</v>
+        <v>99120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>517650</v>
+        <v>517637</v>
       </c>
       <c r="R34" t="n">
-        <v>7054421</v>
+        <v>7054435</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3977,12 +4004,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4002,7 +4029,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Erik Borgström</t>
+          <t>Erik Borgström, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4013,10 +4040,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128711227</v>
+        <v>128710866</v>
       </c>
       <c r="B35" t="n">
-        <v>98595</v>
+        <v>99120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,21 +4051,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4075,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517647</v>
+        <v>517632</v>
       </c>
       <c r="R35" t="n">
-        <v>7054446</v>
+        <v>7054437</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4078,12 +4105,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4114,10 +4141,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128711257</v>
+        <v>128710870</v>
       </c>
       <c r="B36" t="n">
-        <v>98701</v>
+        <v>99120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,21 +4152,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4149,10 +4176,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517654</v>
+        <v>517632</v>
       </c>
       <c r="R36" t="n">
-        <v>7054407</v>
+        <v>7054434</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4179,12 +4206,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4215,48 +4242,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130055222</v>
+        <v>128710873</v>
       </c>
       <c r="B37" t="n">
-        <v>97857</v>
+        <v>99120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222112</v>
+        <v>219811</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hammerdal-Strömsund, Jmt</t>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517651</v>
+        <v>517629</v>
       </c>
       <c r="R37" t="n">
-        <v>7054471</v>
+        <v>7054432</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4280,22 +4307,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4306,24 +4323,6700 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128710876</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>517635</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7054428</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128710879</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7054427</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128710882</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7054424</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128710886</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7054422</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128710887</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>517632</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7054418</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128710888</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>517636</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7054415</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128710893</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7054416</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128710895</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>517638</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7054409</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128710897</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>517636</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7054412</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128711219</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>517646</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7054461</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128711229</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>517648</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7054440</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128711231</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>517647</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7054439</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128711232</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>517647</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7054436</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128711233</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>517650</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7054437</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128711236</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>517648</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7054434</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128711241</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>517648</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7054429</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128711243</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>517649</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7054428</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128711244</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>517650</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7054421</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128711246</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>517650</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7054419</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128711247</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>517656</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7054411</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128711249</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>517650</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7054415</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128711253</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7054411</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128711254</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>517653</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7054414</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128711255</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>517658</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7054404</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128711256</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>517653</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7054410</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128711259</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>517652</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7054391</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128711260</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>517656</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7054401</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128711263</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>517659</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7054360</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128711266</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>517656</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7054391</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128711268</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7054385</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128711269</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>517652</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7054387</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128711272</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7054407</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128711273</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7054404</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128710849</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>517634</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7054446</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128710850</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>517629</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7054449</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128710852</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>517630</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7054448</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128710854</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>517631</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7054446</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128710857</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>517628</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7054440</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128710861</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7054443</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128710871</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>517630</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7054433</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128710872</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>517634</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7054434</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128710875</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7054430</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128710878</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>517635</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7054428</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128710883</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7054422</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128710885</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>517634</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7054421</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128710891</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>517637</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7054411</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128710892</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>517634</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7054418</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128710894</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>517635</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7054413</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128710896</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>517634</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7054406</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128711217</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>517646</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7054465</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128711220</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>517649</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7054461</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128711226</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>517649</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7054451</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128711235</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>517650</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7054437</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128711250</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>517655</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7054413</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128711251</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>517654</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7054417</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128711257</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>517654</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7054407</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128711258</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>517656</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7054401</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128711261</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>517656</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7054364</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128711264</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>517658</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7054379</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128711265</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>517657</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7054379</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128711271</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>517655</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7054394</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Erik Borgström, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128710889</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>517632</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7054419</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128710890</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>517633</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7054419</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128711216</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>E45 mellan Strömsund och väg 344, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>517649</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7054471</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Magnus Lundin, Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>130055222</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Hammerdal-Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>517651</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7054471</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
           <t>Erik Borgström</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>Erik Borgström</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>96281000</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hammerdal- Hallviken- Strömsund, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>517649</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7054362</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Tomas Axelson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4579-2024 artfynd.xlsx
+++ b/artfynd/A 4579-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125950641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711270</t>
         </is>
       </c>
     </row>
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133021108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710851</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710860</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710867</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710868</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710874</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710877</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710880</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710884</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711218</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711221</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711223</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711224</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711225</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2724,6 +2824,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711227</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711228</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711230</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711237</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3128,6 +3248,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711238</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3229,6 +3354,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711239</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3330,6 +3460,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711242</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3431,6 +3566,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711245</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3532,6 +3672,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711252</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3633,6 +3778,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3734,6 +3884,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710858</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3835,6 +3990,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710859</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710862</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4037,6 +4202,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710863</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4138,6 +4308,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710866</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4239,6 +4414,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710870</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4340,6 +4520,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710873</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4441,6 +4626,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710876</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710879</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4643,6 +4838,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710882</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4744,6 +4944,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710886</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4845,6 +5050,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710887</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710888</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5047,6 +5262,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710893</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710895</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5249,6 +5474,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710897</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5350,6 +5580,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711219</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5451,6 +5686,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711229</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5552,6 +5792,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711231</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5653,6 +5898,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711232</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5754,6 +6004,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711233</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5855,6 +6110,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711236</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5956,6 +6216,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711241</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6057,6 +6322,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711243</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6158,6 +6428,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711244</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6259,6 +6534,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711246</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6360,6 +6640,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711247</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6461,6 +6746,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711249</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6562,6 +6852,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711253</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6663,6 +6958,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711254</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6764,6 +7064,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711255</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6865,6 +7170,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711256</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6966,6 +7276,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711259</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7067,6 +7382,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711260</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7168,6 +7488,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711263</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7269,6 +7594,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711266</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7370,6 +7700,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711268</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7471,6 +7806,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711269</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7572,6 +7912,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711272</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7673,6 +8018,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711273</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7774,6 +8124,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710849</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7875,6 +8230,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710850</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7976,6 +8336,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710852</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8077,6 +8442,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710854</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8178,6 +8548,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710857</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8279,6 +8654,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710861</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8380,6 +8760,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710871</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8481,6 +8866,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710872</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8582,6 +8972,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710875</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8683,6 +9078,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710878</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8784,6 +9184,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710883</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8885,6 +9290,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710885</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8986,6 +9396,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710891</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9087,6 +9502,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710892</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9188,6 +9608,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710894</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9289,6 +9714,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710896</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9390,6 +9820,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711217</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9491,6 +9926,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711220</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9592,6 +10032,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711226</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9693,6 +10138,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711235</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9794,6 +10244,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711250</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9895,6 +10350,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711251</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9996,6 +10456,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711257</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10097,6 +10562,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711258</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10198,6 +10668,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711261</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10299,6 +10774,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711264</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10400,6 +10880,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711265</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10501,6 +10986,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711271</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10602,6 +11092,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710889</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10703,6 +11198,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128710890</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10804,6 +11304,11 @@
           <t>C250138 Dikesinventering Jämtland 2025</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128711216</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10916,6 +11421,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130055222</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11017,8 +11527,117 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96281000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>